--- a/BOM/Template 2.xlsx
+++ b/BOM/Template 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DANIEL\ANTIGRAVITY\PROJEK\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7517BB-32E6-4C90-9AF6-3165BAD31277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D528861-8A70-43B8-872D-5224DDB3AE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5480" yWindow="3460" windowWidth="14400" windowHeight="7300" xr2:uid="{875B0192-E6D7-42F7-91CE-44195EEB0615}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{875B0192-E6D7-42F7-91CE-44195EEB0615}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -512,47 +512,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -634,6 +595,45 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -957,3383 +957,3469 @@
   <dimension ref="A1:AK39"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.453125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.90625" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.90625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="4.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" style="13"/>
-    <col min="13" max="14" width="4.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7265625" style="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.90625" style="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.90625" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="59.7265625" style="13" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.26953125" style="13" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.26953125" style="13" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="8.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.6328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="5.7265625" style="13" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.90625" style="13" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.26953125" style="13" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.90625" style="13" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.08984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="21.26953125" style="13" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="8.7265625" style="13"/>
+    <col min="1" max="1" width="10.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="4.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" style="2"/>
+    <col min="13" max="14" width="4.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="59.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="8.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="3.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="21.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="1" t="s">
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="X1" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="Z1" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AA1" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB1" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AC1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AD1" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AE1" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="10" t="s">
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="AI1" s="11" t="s">
+      <c r="AI1" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="AJ1" s="12" t="s">
+      <c r="AJ1" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="AK1" s="12" t="s">
+      <c r="AK1" s="31" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="15" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="32"/>
+      <c r="H2" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15" t="s">
+      <c r="I2" s="32"/>
+      <c r="J2" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="17" t="s">
+      <c r="K2" s="32"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
-      <c r="AH2" s="10"/>
-      <c r="AI2" s="11"/>
-      <c r="AJ2" s="12"/>
-      <c r="AK2" s="12"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="39"/>
+      <c r="Z2" s="39"/>
+      <c r="AA2" s="33"/>
+      <c r="AB2" s="33"/>
+      <c r="AC2" s="34"/>
+      <c r="AD2" s="34"/>
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="31"/>
+      <c r="AK2" s="31"/>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
-      <c r="T3" s="18"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="19"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="19"/>
-      <c r="Z3" s="19"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="22"/>
-      <c r="AC3" s="22"/>
-      <c r="AD3" s="23"/>
-      <c r="AE3" s="24"/>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="23"/>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="25"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="11"/>
+      <c r="AF3" s="12"/>
+      <c r="AG3" s="12"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="13"/>
+      <c r="AJ3" s="14"/>
+      <c r="AK3" s="12"/>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" s="21">
+      <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="12">
         <v>20323076</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19">
+      <c r="F4" s="16"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6">
         <v>19</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="6">
         <v>320</v>
       </c>
-      <c r="O4" s="19">
+      <c r="O4" s="6">
         <v>2434</v>
       </c>
-      <c r="P4" s="19">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="25">
-        <v>2</v>
-      </c>
-      <c r="R4" s="30"/>
-      <c r="S4" s="31" t="s">
+      <c r="P4" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>2</v>
+      </c>
+      <c r="R4" s="17"/>
+      <c r="S4" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="T4" s="31" t="s">
+      <c r="T4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="U4" s="19" t="s">
+      <c r="U4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="V4" s="20" t="s">
+      <c r="V4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="W4" s="19"/>
-      <c r="X4" s="21"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="22">
+      <c r="W4" s="6"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA4" s="9">
         <v>2.9597439999999999E-2</v>
       </c>
-      <c r="AB4" s="22">
+      <c r="AB4" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AC4" s="22">
+      <c r="AC4" s="9">
         <v>2.9597439999999999E-2</v>
       </c>
-      <c r="AD4" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE4" s="24">
+      <c r="AD4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE4" s="11">
         <v>1479.85720128</v>
       </c>
-      <c r="AF4" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG4" s="25">
+      <c r="AF4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG4" s="12">
         <v>99999</v>
       </c>
-      <c r="AH4" s="23" t="s">
+      <c r="AH4" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI4" s="26"/>
-      <c r="AJ4" s="27"/>
-      <c r="AK4" s="25"/>
+      <c r="AI4" s="13"/>
+      <c r="AJ4" s="14"/>
+      <c r="AK4" s="12"/>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" s="32"/>
-      <c r="B5" s="33" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="12">
         <v>20323077</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="34"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="35">
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="22">
         <v>19</v>
       </c>
-      <c r="N5" s="35">
+      <c r="N5" s="22">
         <v>320</v>
       </c>
-      <c r="O5" s="35">
+      <c r="O5" s="22">
         <v>2434</v>
       </c>
-      <c r="P5" s="35">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="25">
-        <v>2</v>
-      </c>
-      <c r="R5" s="36"/>
-      <c r="S5" s="37" t="s">
+      <c r="P5" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>2</v>
+      </c>
+      <c r="R5" s="23"/>
+      <c r="S5" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="T5" s="31"/>
-      <c r="U5" s="25" t="s">
+      <c r="T5" s="18"/>
+      <c r="U5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="V5" s="25" t="s">
+      <c r="V5" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W5" s="24"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="39"/>
-      <c r="Z5" s="19"/>
-      <c r="AA5" s="22">
+      <c r="W5" s="11"/>
+      <c r="X5" s="25"/>
+      <c r="Y5" s="26"/>
+      <c r="Z5" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA5" s="9">
         <v>2.9597439999999999E-2</v>
       </c>
-      <c r="AB5" s="22">
+      <c r="AB5" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AC5" s="22">
+      <c r="AC5" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AD5" s="25" t="s">
+      <c r="AD5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE5" s="24">
+      <c r="AE5" s="11">
         <v>1479.85720128</v>
       </c>
-      <c r="AF5" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG5" s="25">
+      <c r="AF5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG5" s="12">
         <v>99999</v>
       </c>
-      <c r="AH5" s="23" t="s">
+      <c r="AH5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI5" s="40"/>
-      <c r="AJ5" s="27"/>
-      <c r="AK5" s="25"/>
+      <c r="AI5" s="27"/>
+      <c r="AJ5" s="14"/>
+      <c r="AK5" s="12"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" s="32"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="19"/>
+      <c r="B6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="12">
         <v>20323078</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="28">
         <v>0</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="12">
         <v>18</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="28">
         <v>10</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="12">
         <v>330</v>
       </c>
-      <c r="J6" s="41">
+      <c r="J6" s="28">
         <v>10</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="12">
         <v>2444</v>
       </c>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25">
+      <c r="L6" s="12"/>
+      <c r="M6" s="12">
         <v>18</v>
       </c>
-      <c r="N6" s="25">
+      <c r="N6" s="12">
         <v>320</v>
       </c>
-      <c r="O6" s="25">
+      <c r="O6" s="12">
         <v>2434</v>
       </c>
-      <c r="P6" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="25">
-        <v>2</v>
-      </c>
-      <c r="R6" s="36">
+      <c r="P6" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>2</v>
+      </c>
+      <c r="R6" s="23">
         <v>2.903472E-2</v>
       </c>
-      <c r="S6" s="37" t="s">
+      <c r="S6" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="T6" s="37"/>
-      <c r="U6" s="25" t="s">
+      <c r="T6" s="24"/>
+      <c r="U6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="V6" s="25" t="s">
+      <c r="V6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W6" s="24"/>
-      <c r="X6" s="38"/>
-      <c r="Y6" s="39"/>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="22">
+      <c r="W6" s="11"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="26"/>
+      <c r="Z6" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA6" s="9">
         <v>2.8039680000000001E-2</v>
       </c>
-      <c r="AB6" s="22">
+      <c r="AB6" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AC6" s="22">
+      <c r="AC6" s="9">
         <v>2.8039680000000001E-2</v>
       </c>
-      <c r="AD6" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE6" s="24">
+      <c r="AD6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE6" s="11">
         <v>1401.96998016</v>
       </c>
-      <c r="AF6" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG6" s="25">
+      <c r="AF6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG6" s="12">
         <v>99999</v>
       </c>
-      <c r="AH6" s="23" t="s">
+      <c r="AH6" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AI6" s="40"/>
-      <c r="AJ6" s="27"/>
-      <c r="AK6" s="25"/>
+      <c r="AI6" s="27"/>
+      <c r="AJ6" s="14"/>
+      <c r="AK6" s="12"/>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="12">
         <v>20323079</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="28">
         <v>0.1</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="12">
         <v>0.6</v>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="29">
         <v>10</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="12">
         <v>330</v>
       </c>
-      <c r="J7" s="42">
+      <c r="J7" s="29">
         <v>10</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="12">
         <v>2444</v>
       </c>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25">
+      <c r="L7" s="12"/>
+      <c r="M7" s="12">
         <v>0.5</v>
       </c>
-      <c r="N7" s="25">
+      <c r="N7" s="12">
         <v>320</v>
       </c>
-      <c r="O7" s="25">
+      <c r="O7" s="12">
         <v>2434</v>
       </c>
-      <c r="P7" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="25">
-        <v>2</v>
-      </c>
-      <c r="R7" s="36"/>
-      <c r="S7" s="37" t="s">
+      <c r="P7" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>2</v>
+      </c>
+      <c r="R7" s="23"/>
+      <c r="S7" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T7" s="31"/>
-      <c r="U7" s="25" t="s">
+      <c r="T7" s="18"/>
+      <c r="U7" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="V7" s="25" t="s">
+      <c r="V7" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W7" s="24"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="22">
+      <c r="W7" s="11"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA7" s="9">
         <v>7.7888000000000002E-4</v>
       </c>
-      <c r="AB7" s="22">
+      <c r="AB7" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AC7" s="22">
+      <c r="AC7" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AD7" s="25" t="s">
+      <c r="AD7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE7" s="24">
+      <c r="AE7" s="11">
         <v>38.943610560000003</v>
       </c>
-      <c r="AF7" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG7" s="25">
+      <c r="AF7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG7" s="12">
         <v>99999</v>
       </c>
-      <c r="AH7" s="23" t="s">
+      <c r="AH7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="AI7" s="40"/>
-      <c r="AJ7" s="27"/>
-      <c r="AK7" s="25"/>
+      <c r="AI7" s="27"/>
+      <c r="AJ7" s="14"/>
+      <c r="AK7" s="12"/>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A8" s="32"/>
-      <c r="B8" s="25" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="12">
         <v>20323080</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="28">
         <v>0.1</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="12">
         <v>0.6</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="28">
         <v>10</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="12">
         <v>330</v>
       </c>
-      <c r="J8" s="41">
+      <c r="J8" s="28">
         <v>10</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="12">
         <v>2444</v>
       </c>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25">
+      <c r="L8" s="12"/>
+      <c r="M8" s="12">
         <v>0.5</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="12">
         <v>320</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="12">
         <v>2434</v>
       </c>
-      <c r="P8" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="25">
-        <v>2</v>
-      </c>
-      <c r="R8" s="36">
+      <c r="P8" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>2</v>
+      </c>
+      <c r="R8" s="23">
         <v>1.61304</v>
       </c>
-      <c r="S8" s="37" t="s">
+      <c r="S8" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T8" s="31"/>
-      <c r="U8" s="25" t="s">
+      <c r="T8" s="18"/>
+      <c r="U8" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="V8" s="25" t="s">
+      <c r="V8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W8" s="24"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="22">
+      <c r="W8" s="11"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA8" s="9">
         <v>7.7888000000000002E-4</v>
       </c>
-      <c r="AB8" s="22">
+      <c r="AB8" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AC8" s="22">
+      <c r="AC8" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AD8" s="25" t="s">
+      <c r="AD8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE8" s="24">
+      <c r="AE8" s="11">
         <v>38.943610560000003</v>
       </c>
-      <c r="AF8" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG8" s="25">
+      <c r="AF8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG8" s="12">
         <v>99999</v>
       </c>
-      <c r="AH8" s="23" t="s">
+      <c r="AH8" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="AI8" s="40"/>
-      <c r="AJ8" s="27"/>
-      <c r="AK8" s="25"/>
+      <c r="AI8" s="27"/>
+      <c r="AJ8" s="14"/>
+      <c r="AK8" s="12"/>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A9" s="21">
-        <v>2</v>
-      </c>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="8">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="12">
         <v>20323081</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19">
+      <c r="F9" s="16"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6">
         <v>19</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="6">
         <v>320</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="6">
         <v>2434</v>
       </c>
-      <c r="P9" s="19">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="25">
-        <v>2</v>
-      </c>
-      <c r="R9" s="30"/>
-      <c r="S9" s="31" t="s">
+      <c r="P9" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>2</v>
+      </c>
+      <c r="R9" s="17"/>
+      <c r="S9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="T9" s="31" t="s">
+      <c r="T9" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="U9" s="19" t="s">
+      <c r="U9" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="V9" s="20" t="s">
+      <c r="V9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="W9" s="19"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="21"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="22">
+      <c r="W9" s="6"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA9" s="9">
         <v>2.9597439999999999E-2</v>
       </c>
-      <c r="AB9" s="22">
+      <c r="AB9" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AC9" s="22">
+      <c r="AC9" s="9">
         <v>2.9597439999999999E-2</v>
       </c>
-      <c r="AD9" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE9" s="24">
+      <c r="AD9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE9" s="11">
         <v>1479.85720128</v>
       </c>
-      <c r="AF9" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG9" s="25">
+      <c r="AF9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG9" s="12">
         <v>99999</v>
       </c>
-      <c r="AH9" s="23" t="s">
+      <c r="AH9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI9" s="26"/>
-      <c r="AJ9" s="27"/>
-      <c r="AK9" s="25"/>
+      <c r="AI9" s="13"/>
+      <c r="AJ9" s="14"/>
+      <c r="AK9" s="12"/>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A10" s="32"/>
-      <c r="B10" s="33" t="s">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="12">
         <v>20323077</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="34"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="35">
+      <c r="F10" s="21"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="22">
         <v>19</v>
       </c>
-      <c r="N10" s="35">
+      <c r="N10" s="22">
         <v>320</v>
       </c>
-      <c r="O10" s="35">
+      <c r="O10" s="22">
         <v>2434</v>
       </c>
-      <c r="P10" s="35">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="25">
-        <v>2</v>
-      </c>
-      <c r="R10" s="36"/>
-      <c r="S10" s="37" t="s">
+      <c r="P10" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>2</v>
+      </c>
+      <c r="R10" s="23"/>
+      <c r="S10" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="T10" s="31"/>
-      <c r="U10" s="25" t="s">
+      <c r="T10" s="18"/>
+      <c r="U10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="V10" s="25" t="s">
+      <c r="V10" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W10" s="24"/>
-      <c r="X10" s="38"/>
-      <c r="Y10" s="39"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="22">
+      <c r="W10" s="11"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="26"/>
+      <c r="Z10" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA10" s="9">
         <v>2.9597439999999999E-2</v>
       </c>
-      <c r="AB10" s="22">
+      <c r="AB10" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AC10" s="22">
+      <c r="AC10" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AD10" s="25" t="s">
+      <c r="AD10" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE10" s="24">
+      <c r="AE10" s="11">
         <v>1479.85720128</v>
       </c>
-      <c r="AF10" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG10" s="25">
+      <c r="AF10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG10" s="12">
         <v>99999</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AH10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI10" s="40"/>
-      <c r="AJ10" s="27"/>
-      <c r="AK10" s="25"/>
+      <c r="AI10" s="27"/>
+      <c r="AJ10" s="14"/>
+      <c r="AK10" s="12"/>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A11" s="32"/>
-      <c r="B11" s="25" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="12">
         <v>20323078</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="28">
         <v>0</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="12">
         <v>18</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="28">
         <v>10</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="12">
         <v>330</v>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="28">
         <v>10</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="12">
         <v>2444</v>
       </c>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25">
+      <c r="L11" s="12"/>
+      <c r="M11" s="12">
         <v>18</v>
       </c>
-      <c r="N11" s="25">
+      <c r="N11" s="12">
         <v>320</v>
       </c>
-      <c r="O11" s="25">
+      <c r="O11" s="12">
         <v>2434</v>
       </c>
-      <c r="P11" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="25">
-        <v>2</v>
-      </c>
-      <c r="R11" s="36">
+      <c r="P11" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>2</v>
+      </c>
+      <c r="R11" s="23">
         <v>2.903472E-2</v>
       </c>
-      <c r="S11" s="37" t="s">
+      <c r="S11" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="T11" s="37"/>
-      <c r="U11" s="25" t="s">
+      <c r="T11" s="24"/>
+      <c r="U11" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="V11" s="25" t="s">
+      <c r="V11" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W11" s="24"/>
-      <c r="X11" s="38"/>
-      <c r="Y11" s="39"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="22">
+      <c r="W11" s="11"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="26"/>
+      <c r="Z11" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA11" s="9">
         <v>2.8039680000000001E-2</v>
       </c>
-      <c r="AB11" s="22">
+      <c r="AB11" s="9">
         <v>1.55776</v>
       </c>
-      <c r="AC11" s="22">
+      <c r="AC11" s="9">
         <v>2.8039680000000001E-2</v>
       </c>
-      <c r="AD11" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE11" s="24">
+      <c r="AD11" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE11" s="11">
         <v>1401.96998016</v>
       </c>
-      <c r="AF11" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG11" s="25">
+      <c r="AF11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG11" s="12">
         <v>99999</v>
       </c>
-      <c r="AH11" s="23" t="s">
+      <c r="AH11" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AI11" s="40"/>
-      <c r="AJ11" s="27"/>
-      <c r="AK11" s="25"/>
+      <c r="AI11" s="27"/>
+      <c r="AJ11" s="14"/>
+      <c r="AK11" s="12"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25" t="s">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="12">
         <v>20323079</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="28">
         <v>0.1</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="12">
         <v>0.6</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="29">
         <v>10</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="12">
         <v>330</v>
       </c>
-      <c r="J12" s="42">
+      <c r="J12" s="29">
         <v>10</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="12">
         <v>2444</v>
       </c>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25">
+      <c r="L12" s="12"/>
+      <c r="M12" s="12">
         <v>0.5</v>
       </c>
-      <c r="N12" s="25">
+      <c r="N12" s="12">
         <v>320</v>
       </c>
-      <c r="O12" s="25">
+      <c r="O12" s="12">
         <v>2434</v>
       </c>
-      <c r="P12" s="25">
+      <c r="P12" s="12">
         <v>4</v>
       </c>
-      <c r="Q12" s="25">
+      <c r="Q12" s="12">
         <v>4</v>
       </c>
-      <c r="R12" s="36"/>
-      <c r="S12" s="37" t="s">
+      <c r="R12" s="23"/>
+      <c r="S12" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T12" s="31"/>
-      <c r="U12" s="25" t="s">
+      <c r="T12" s="18"/>
+      <c r="U12" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="V12" s="25" t="s">
+      <c r="V12" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W12" s="24"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="22">
+      <c r="W12" s="11"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA12" s="9">
         <v>1.55776E-3</v>
       </c>
-      <c r="AB12" s="22">
+      <c r="AB12" s="9">
         <v>3.1155200000000001</v>
       </c>
-      <c r="AC12" s="22">
+      <c r="AC12" s="9">
         <v>3.1155200000000001</v>
       </c>
-      <c r="AD12" s="25" t="s">
+      <c r="AD12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE12" s="24">
+      <c r="AE12" s="11">
         <v>38.943610560000003</v>
       </c>
-      <c r="AF12" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG12" s="25">
+      <c r="AF12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG12" s="12">
         <v>99999</v>
       </c>
-      <c r="AH12" s="23" t="s">
+      <c r="AH12" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="AI12" s="40"/>
-      <c r="AJ12" s="27"/>
-      <c r="AK12" s="25"/>
+      <c r="AI12" s="27"/>
+      <c r="AJ12" s="14"/>
+      <c r="AK12" s="12"/>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
-      <c r="B13" s="25" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="12">
         <v>20323080</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="28">
         <v>0.1</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="12">
         <v>0.6</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="28">
         <v>10</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="12">
         <v>330</v>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="28">
         <v>10</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="12">
         <v>2444</v>
       </c>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25">
+      <c r="L13" s="12"/>
+      <c r="M13" s="12">
         <v>0.5</v>
       </c>
-      <c r="N13" s="25">
+      <c r="N13" s="12">
         <v>320</v>
       </c>
-      <c r="O13" s="25">
+      <c r="O13" s="12">
         <v>2434</v>
       </c>
-      <c r="P13" s="25">
+      <c r="P13" s="12">
         <v>4</v>
       </c>
-      <c r="Q13" s="25">
+      <c r="Q13" s="12">
         <v>4</v>
       </c>
-      <c r="R13" s="36">
+      <c r="R13" s="23">
         <v>3.2260800000000001</v>
       </c>
-      <c r="S13" s="37" t="s">
+      <c r="S13" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T13" s="31"/>
-      <c r="U13" s="25" t="s">
+      <c r="T13" s="18"/>
+      <c r="U13" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="V13" s="25" t="s">
+      <c r="V13" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W13" s="24"/>
-      <c r="X13" s="38"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="22">
+      <c r="W13" s="11"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA13" s="9">
         <v>1.55776E-3</v>
       </c>
-      <c r="AB13" s="22">
+      <c r="AB13" s="9">
         <v>3.1155200000000001</v>
       </c>
-      <c r="AC13" s="22">
+      <c r="AC13" s="9">
         <v>3.1155200000000001</v>
       </c>
-      <c r="AD13" s="25" t="s">
+      <c r="AD13" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE13" s="24">
+      <c r="AE13" s="11">
         <v>38.943610560000003</v>
       </c>
-      <c r="AF13" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG13" s="25">
+      <c r="AF13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG13" s="12">
         <v>99999</v>
       </c>
-      <c r="AH13" s="23" t="s">
+      <c r="AH13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="AI13" s="40"/>
-      <c r="AJ13" s="27"/>
-      <c r="AK13" s="25"/>
+      <c r="AI13" s="27"/>
+      <c r="AJ13" s="14"/>
+      <c r="AK13" s="12"/>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
+      <c r="A14" s="8">
         <v>3</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="12">
         <v>20323082</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19">
+      <c r="F14" s="16"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6">
         <v>19</v>
       </c>
-      <c r="N14" s="19">
+      <c r="N14" s="6">
         <v>110</v>
       </c>
-      <c r="O14" s="19">
+      <c r="O14" s="6">
         <v>2434</v>
       </c>
-      <c r="P14" s="19">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="25">
-        <v>2</v>
-      </c>
-      <c r="R14" s="30"/>
-      <c r="S14" s="31" t="s">
+      <c r="P14" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>2</v>
+      </c>
+      <c r="R14" s="17"/>
+      <c r="S14" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="T14" s="31" t="s">
+      <c r="T14" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="U14" s="19" t="s">
+      <c r="U14" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="V14" s="20" t="s">
+      <c r="V14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="W14" s="19"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="21"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="22">
+      <c r="W14" s="6"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA14" s="9">
         <v>1.017412E-2</v>
       </c>
-      <c r="AB14" s="22">
+      <c r="AB14" s="9">
         <v>0.53547999999999996</v>
       </c>
-      <c r="AC14" s="22">
+      <c r="AC14" s="9">
         <v>1.017412E-2</v>
       </c>
-      <c r="AD14" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE14" s="24">
+      <c r="AD14" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE14" s="11">
         <v>508.70091294000002</v>
       </c>
-      <c r="AF14" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG14" s="25">
+      <c r="AF14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG14" s="12">
         <v>99999</v>
       </c>
-      <c r="AH14" s="23" t="s">
+      <c r="AH14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI14" s="26"/>
-      <c r="AJ14" s="27"/>
-      <c r="AK14" s="25"/>
+      <c r="AI14" s="13"/>
+      <c r="AJ14" s="14"/>
+      <c r="AK14" s="12"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
-      <c r="B15" s="33" t="s">
+      <c r="A15" s="19"/>
+      <c r="B15" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="12">
         <v>20323083</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="35">
+      <c r="F15" s="21"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="22">
         <v>19</v>
       </c>
-      <c r="N15" s="35">
+      <c r="N15" s="22">
         <v>110</v>
       </c>
-      <c r="O15" s="35">
+      <c r="O15" s="22">
         <v>2434</v>
       </c>
-      <c r="P15" s="35">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="25">
-        <v>2</v>
-      </c>
-      <c r="R15" s="36"/>
-      <c r="S15" s="37" t="s">
+      <c r="P15" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>2</v>
+      </c>
+      <c r="R15" s="23"/>
+      <c r="S15" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="T15" s="31"/>
-      <c r="U15" s="25" t="s">
+      <c r="T15" s="18"/>
+      <c r="U15" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="V15" s="25" t="s">
+      <c r="V15" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W15" s="24"/>
-      <c r="X15" s="38"/>
-      <c r="Y15" s="39"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="22">
+      <c r="W15" s="11"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA15" s="9">
         <v>1.017412E-2</v>
       </c>
-      <c r="AB15" s="22">
+      <c r="AB15" s="9">
         <v>0.53547999999999996</v>
       </c>
-      <c r="AC15" s="22">
+      <c r="AC15" s="9">
         <v>0.53547999999999996</v>
       </c>
-      <c r="AD15" s="25" t="s">
+      <c r="AD15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE15" s="24">
+      <c r="AE15" s="11">
         <v>508.70091294000002</v>
       </c>
-      <c r="AF15" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG15" s="25">
+      <c r="AF15" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG15" s="12">
         <v>99999</v>
       </c>
-      <c r="AH15" s="23" t="s">
+      <c r="AH15" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI15" s="40"/>
-      <c r="AJ15" s="27"/>
-      <c r="AK15" s="25"/>
+      <c r="AI15" s="27"/>
+      <c r="AJ15" s="14"/>
+      <c r="AK15" s="12"/>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
-      <c r="B16" s="25" t="s">
+      <c r="A16" s="19"/>
+      <c r="B16" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="12">
         <v>20323084</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="28">
         <v>0</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="12">
         <v>18</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="28">
         <v>10</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="12">
         <v>120</v>
       </c>
-      <c r="J16" s="41">
+      <c r="J16" s="28">
         <v>10</v>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="12">
         <v>2444</v>
       </c>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25">
+      <c r="L16" s="12"/>
+      <c r="M16" s="12">
         <v>18</v>
       </c>
-      <c r="N16" s="25">
+      <c r="N16" s="12">
         <v>110</v>
       </c>
-      <c r="O16" s="25">
+      <c r="O16" s="12">
         <v>2434</v>
       </c>
-      <c r="P16" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="25">
-        <v>2</v>
-      </c>
-      <c r="R16" s="36">
+      <c r="P16" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>2</v>
+      </c>
+      <c r="R16" s="23">
         <v>1.0558079999999999E-2</v>
       </c>
-      <c r="S16" s="37" t="s">
+      <c r="S16" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="T16" s="37"/>
-      <c r="U16" s="25" t="s">
+      <c r="T16" s="24"/>
+      <c r="U16" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="V16" s="25" t="s">
+      <c r="V16" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W16" s="24"/>
-      <c r="X16" s="38"/>
-      <c r="Y16" s="39"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="22">
+      <c r="W16" s="11"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA16" s="9">
         <v>9.6386400000000004E-3</v>
       </c>
-      <c r="AB16" s="22">
+      <c r="AB16" s="9">
         <v>0.53547999999999996</v>
       </c>
-      <c r="AC16" s="22">
+      <c r="AC16" s="9">
         <v>9.6386400000000004E-3</v>
       </c>
-      <c r="AD16" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE16" s="24">
+      <c r="AD16" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE16" s="11">
         <v>481.92718067999999</v>
       </c>
-      <c r="AF16" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG16" s="25">
+      <c r="AF16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG16" s="12">
         <v>99999</v>
       </c>
-      <c r="AH16" s="23" t="s">
+      <c r="AH16" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="40"/>
-      <c r="AJ16" s="27"/>
-      <c r="AK16" s="25"/>
+      <c r="AI16" s="27"/>
+      <c r="AJ16" s="14"/>
+      <c r="AK16" s="12"/>
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25" t="s">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="12">
         <v>20323085</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="28">
         <v>0.1</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="12">
         <v>0.6</v>
       </c>
-      <c r="H17" s="42">
+      <c r="H17" s="29">
         <v>10</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="12">
         <v>120</v>
       </c>
-      <c r="J17" s="42">
+      <c r="J17" s="29">
         <v>10</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="12">
         <v>2444</v>
       </c>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25">
+      <c r="L17" s="12"/>
+      <c r="M17" s="12">
         <v>0.5</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="12">
         <v>110</v>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="12">
         <v>2434</v>
       </c>
-      <c r="P17" s="25">
+      <c r="P17" s="12">
         <v>4</v>
       </c>
-      <c r="Q17" s="25">
+      <c r="Q17" s="12">
         <v>4</v>
       </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="37" t="s">
+      <c r="R17" s="23"/>
+      <c r="S17" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T17" s="31"/>
-      <c r="U17" s="25" t="s">
+      <c r="T17" s="18"/>
+      <c r="U17" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="V17" s="25" t="s">
+      <c r="V17" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W17" s="24"/>
-      <c r="X17" s="38"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="22">
+      <c r="W17" s="11"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA17" s="9">
         <v>5.3547999999999996E-4</v>
       </c>
-      <c r="AB17" s="22">
+      <c r="AB17" s="9">
         <v>1.0709599999999999</v>
       </c>
-      <c r="AC17" s="22">
+      <c r="AC17" s="9">
         <v>1.0709599999999999</v>
       </c>
-      <c r="AD17" s="25" t="s">
+      <c r="AD17" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE17" s="24">
+      <c r="AE17" s="11">
         <v>13.38686613</v>
       </c>
-      <c r="AF17" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG17" s="25">
+      <c r="AF17" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG17" s="12">
         <v>99999</v>
       </c>
-      <c r="AH17" s="23" t="s">
+      <c r="AH17" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AI17" s="40"/>
-      <c r="AJ17" s="27"/>
-      <c r="AK17" s="25"/>
+      <c r="AI17" s="27"/>
+      <c r="AJ17" s="14"/>
+      <c r="AK17" s="12"/>
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A18" s="32"/>
-      <c r="B18" s="25" t="s">
+      <c r="A18" s="19"/>
+      <c r="B18" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="12">
         <v>20323086</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="28">
         <v>0.1</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="12">
         <v>0.6</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="28">
         <v>10</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="12">
         <v>120</v>
       </c>
-      <c r="J18" s="41">
+      <c r="J18" s="28">
         <v>10</v>
       </c>
-      <c r="K18" s="25">
+      <c r="K18" s="12">
         <v>2444</v>
       </c>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25">
+      <c r="L18" s="12"/>
+      <c r="M18" s="12">
         <v>0.5</v>
       </c>
-      <c r="N18" s="25">
+      <c r="N18" s="12">
         <v>110</v>
       </c>
-      <c r="O18" s="25">
+      <c r="O18" s="12">
         <v>2434</v>
       </c>
-      <c r="P18" s="25">
+      <c r="P18" s="12">
         <v>4</v>
       </c>
-      <c r="Q18" s="25">
+      <c r="Q18" s="12">
         <v>4</v>
       </c>
-      <c r="R18" s="36">
+      <c r="R18" s="23">
         <v>1.1731199999999999</v>
       </c>
-      <c r="S18" s="37" t="s">
+      <c r="S18" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T18" s="31"/>
-      <c r="U18" s="25" t="s">
+      <c r="T18" s="18"/>
+      <c r="U18" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="V18" s="25" t="s">
+      <c r="V18" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W18" s="24"/>
-      <c r="X18" s="38"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="22">
+      <c r="W18" s="11"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA18" s="9">
         <v>5.3547999999999996E-4</v>
       </c>
-      <c r="AB18" s="22">
+      <c r="AB18" s="9">
         <v>1.0709599999999999</v>
       </c>
-      <c r="AC18" s="22">
+      <c r="AC18" s="9">
         <v>1.0709599999999999</v>
       </c>
-      <c r="AD18" s="25" t="s">
+      <c r="AD18" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE18" s="24">
+      <c r="AE18" s="11">
         <v>13.38686613</v>
       </c>
-      <c r="AF18" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG18" s="25">
+      <c r="AF18" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG18" s="12">
         <v>99999</v>
       </c>
-      <c r="AH18" s="23" t="s">
+      <c r="AH18" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AI18" s="40"/>
-      <c r="AJ18" s="27"/>
-      <c r="AK18" s="25"/>
+      <c r="AI18" s="27"/>
+      <c r="AJ18" s="14"/>
+      <c r="AK18" s="12"/>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A19" s="21">
+      <c r="A19" s="8">
         <v>4</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="12">
         <v>20323087</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="29"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19">
+      <c r="F19" s="16"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6">
         <v>19</v>
       </c>
-      <c r="N19" s="19">
+      <c r="N19" s="6">
         <v>110</v>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="6">
         <v>2434</v>
       </c>
-      <c r="P19" s="19">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="25">
-        <v>2</v>
-      </c>
-      <c r="R19" s="30"/>
-      <c r="S19" s="31" t="s">
+      <c r="P19" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="12">
+        <v>2</v>
+      </c>
+      <c r="R19" s="17"/>
+      <c r="S19" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="T19" s="31" t="s">
+      <c r="T19" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="U19" s="19" t="s">
+      <c r="U19" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="V19" s="20" t="s">
+      <c r="V19" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="W19" s="19"/>
-      <c r="X19" s="21"/>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="22">
+      <c r="W19" s="6"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA19" s="9">
         <v>1.017412E-2</v>
       </c>
-      <c r="AB19" s="22">
+      <c r="AB19" s="9">
         <v>0.53547999999999996</v>
       </c>
-      <c r="AC19" s="22">
+      <c r="AC19" s="9">
         <v>1.017412E-2</v>
       </c>
-      <c r="AD19" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE19" s="24">
+      <c r="AD19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE19" s="11">
         <v>508.70091294000002</v>
       </c>
-      <c r="AF19" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG19" s="25">
+      <c r="AF19" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG19" s="12">
         <v>99999</v>
       </c>
-      <c r="AH19" s="23" t="s">
+      <c r="AH19" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI19" s="26"/>
-      <c r="AJ19" s="27"/>
-      <c r="AK19" s="25"/>
+      <c r="AI19" s="13"/>
+      <c r="AJ19" s="14"/>
+      <c r="AK19" s="12"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A20" s="32"/>
-      <c r="B20" s="33" t="s">
+      <c r="A20" s="19"/>
+      <c r="B20" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="12">
         <v>20323083</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="34"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="35">
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="22">
         <v>19</v>
       </c>
-      <c r="N20" s="35">
+      <c r="N20" s="22">
         <v>110</v>
       </c>
-      <c r="O20" s="35">
+      <c r="O20" s="22">
         <v>2434</v>
       </c>
-      <c r="P20" s="35">
-        <v>2</v>
-      </c>
-      <c r="Q20" s="25">
-        <v>2</v>
-      </c>
-      <c r="R20" s="36"/>
-      <c r="S20" s="37" t="s">
+      <c r="P20" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="12">
+        <v>2</v>
+      </c>
+      <c r="R20" s="23"/>
+      <c r="S20" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="T20" s="31"/>
-      <c r="U20" s="25" t="s">
+      <c r="T20" s="18"/>
+      <c r="U20" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="V20" s="25" t="s">
+      <c r="V20" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W20" s="24"/>
-      <c r="X20" s="38"/>
-      <c r="Y20" s="39"/>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="22">
+      <c r="W20" s="11"/>
+      <c r="X20" s="25"/>
+      <c r="Y20" s="26"/>
+      <c r="Z20" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA20" s="9">
         <v>1.017412E-2</v>
       </c>
-      <c r="AB20" s="22">
+      <c r="AB20" s="9">
         <v>0.53547999999999996</v>
       </c>
-      <c r="AC20" s="22">
+      <c r="AC20" s="9">
         <v>0.53547999999999996</v>
       </c>
-      <c r="AD20" s="25" t="s">
+      <c r="AD20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE20" s="24">
+      <c r="AE20" s="11">
         <v>508.70091294000002</v>
       </c>
-      <c r="AF20" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG20" s="25">
+      <c r="AF20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG20" s="12">
         <v>99999</v>
       </c>
-      <c r="AH20" s="23" t="s">
+      <c r="AH20" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI20" s="40"/>
-      <c r="AJ20" s="27"/>
-      <c r="AK20" s="25"/>
+      <c r="AI20" s="27"/>
+      <c r="AJ20" s="14"/>
+      <c r="AK20" s="12"/>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A21" s="32"/>
-      <c r="B21" s="25" t="s">
+      <c r="A21" s="19"/>
+      <c r="B21" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="12">
         <v>20323084</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="41">
+      <c r="F21" s="28">
         <v>0</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="12">
         <v>18</v>
       </c>
-      <c r="H21" s="41">
+      <c r="H21" s="28">
         <v>10</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="12">
         <v>120</v>
       </c>
-      <c r="J21" s="41">
+      <c r="J21" s="28">
         <v>10</v>
       </c>
-      <c r="K21" s="25">
+      <c r="K21" s="12">
         <v>2444</v>
       </c>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25">
+      <c r="L21" s="12"/>
+      <c r="M21" s="12">
         <v>18</v>
       </c>
-      <c r="N21" s="25">
+      <c r="N21" s="12">
         <v>110</v>
       </c>
-      <c r="O21" s="25">
+      <c r="O21" s="12">
         <v>2434</v>
       </c>
-      <c r="P21" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q21" s="25">
-        <v>2</v>
-      </c>
-      <c r="R21" s="36">
+      <c r="P21" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="12">
+        <v>2</v>
+      </c>
+      <c r="R21" s="23">
         <v>1.0558079999999999E-2</v>
       </c>
-      <c r="S21" s="37" t="s">
+      <c r="S21" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="T21" s="37"/>
-      <c r="U21" s="25" t="s">
+      <c r="T21" s="24"/>
+      <c r="U21" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="V21" s="25" t="s">
+      <c r="V21" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W21" s="24"/>
-      <c r="X21" s="38"/>
-      <c r="Y21" s="39"/>
-      <c r="Z21" s="19"/>
-      <c r="AA21" s="22">
+      <c r="W21" s="11"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="26"/>
+      <c r="Z21" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA21" s="9">
         <v>9.6386400000000004E-3</v>
       </c>
-      <c r="AB21" s="22">
+      <c r="AB21" s="9">
         <v>0.53547999999999996</v>
       </c>
-      <c r="AC21" s="22">
+      <c r="AC21" s="9">
         <v>9.6386400000000004E-3</v>
       </c>
-      <c r="AD21" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE21" s="24">
+      <c r="AD21" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE21" s="11">
         <v>481.92718067999999</v>
       </c>
-      <c r="AF21" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG21" s="25">
+      <c r="AF21" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG21" s="12">
         <v>99999</v>
       </c>
-      <c r="AH21" s="23" t="s">
+      <c r="AH21" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AI21" s="40"/>
-      <c r="AJ21" s="27"/>
-      <c r="AK21" s="25"/>
+      <c r="AI21" s="27"/>
+      <c r="AJ21" s="14"/>
+      <c r="AK21" s="12"/>
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25" t="s">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="12">
         <v>20323085</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="41">
+      <c r="F22" s="28">
         <v>0.1</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="12">
         <v>0.6</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="29">
         <v>10</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="12">
         <v>120</v>
       </c>
-      <c r="J22" s="42">
+      <c r="J22" s="29">
         <v>10</v>
       </c>
-      <c r="K22" s="25">
+      <c r="K22" s="12">
         <v>2444</v>
       </c>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25">
+      <c r="L22" s="12"/>
+      <c r="M22" s="12">
         <v>0.5</v>
       </c>
-      <c r="N22" s="25">
+      <c r="N22" s="12">
         <v>110</v>
       </c>
-      <c r="O22" s="25">
+      <c r="O22" s="12">
         <v>2434</v>
       </c>
-      <c r="P22" s="25">
+      <c r="P22" s="12">
         <v>4</v>
       </c>
-      <c r="Q22" s="25">
+      <c r="Q22" s="12">
         <v>4</v>
       </c>
-      <c r="R22" s="36"/>
-      <c r="S22" s="37" t="s">
+      <c r="R22" s="23"/>
+      <c r="S22" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T22" s="31"/>
-      <c r="U22" s="25" t="s">
+      <c r="T22" s="18"/>
+      <c r="U22" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="V22" s="25" t="s">
+      <c r="V22" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W22" s="24"/>
-      <c r="X22" s="38"/>
-      <c r="Y22" s="23"/>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="22">
+      <c r="W22" s="11"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="10"/>
+      <c r="Z22" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA22" s="9">
         <v>5.3547999999999996E-4</v>
       </c>
-      <c r="AB22" s="22">
+      <c r="AB22" s="9">
         <v>1.0709599999999999</v>
       </c>
-      <c r="AC22" s="22">
+      <c r="AC22" s="9">
         <v>1.0709599999999999</v>
       </c>
-      <c r="AD22" s="25" t="s">
+      <c r="AD22" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE22" s="24">
+      <c r="AE22" s="11">
         <v>13.38686613</v>
       </c>
-      <c r="AF22" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG22" s="25">
+      <c r="AF22" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG22" s="12">
         <v>99999</v>
       </c>
-      <c r="AH22" s="23" t="s">
+      <c r="AH22" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AI22" s="40"/>
-      <c r="AJ22" s="27"/>
-      <c r="AK22" s="25"/>
+      <c r="AI22" s="27"/>
+      <c r="AJ22" s="14"/>
+      <c r="AK22" s="12"/>
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A23" s="32"/>
-      <c r="B23" s="25" t="s">
+      <c r="A23" s="19"/>
+      <c r="B23" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="12">
         <v>20323086</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="28">
         <v>0.1</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="12">
         <v>0.6</v>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="28">
         <v>10</v>
       </c>
-      <c r="I23" s="25">
+      <c r="I23" s="12">
         <v>120</v>
       </c>
-      <c r="J23" s="41">
+      <c r="J23" s="28">
         <v>10</v>
       </c>
-      <c r="K23" s="25">
+      <c r="K23" s="12">
         <v>2444</v>
       </c>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25">
+      <c r="L23" s="12"/>
+      <c r="M23" s="12">
         <v>0.5</v>
       </c>
-      <c r="N23" s="25">
+      <c r="N23" s="12">
         <v>110</v>
       </c>
-      <c r="O23" s="25">
+      <c r="O23" s="12">
         <v>2434</v>
       </c>
-      <c r="P23" s="25">
+      <c r="P23" s="12">
         <v>4</v>
       </c>
-      <c r="Q23" s="25">
+      <c r="Q23" s="12">
         <v>4</v>
       </c>
-      <c r="R23" s="36">
+      <c r="R23" s="23">
         <v>1.1731199999999999</v>
       </c>
-      <c r="S23" s="37" t="s">
+      <c r="S23" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T23" s="31"/>
-      <c r="U23" s="25" t="s">
+      <c r="T23" s="18"/>
+      <c r="U23" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="V23" s="25" t="s">
+      <c r="V23" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W23" s="24"/>
-      <c r="X23" s="38"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="19"/>
-      <c r="AA23" s="22">
+      <c r="W23" s="11"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA23" s="9">
         <v>5.3547999999999996E-4</v>
       </c>
-      <c r="AB23" s="22">
+      <c r="AB23" s="9">
         <v>1.0709599999999999</v>
       </c>
-      <c r="AC23" s="22">
+      <c r="AC23" s="9">
         <v>1.0709599999999999</v>
       </c>
-      <c r="AD23" s="25" t="s">
+      <c r="AD23" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE23" s="24">
+      <c r="AE23" s="11">
         <v>13.38686613</v>
       </c>
-      <c r="AF23" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG23" s="25">
+      <c r="AF23" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG23" s="12">
         <v>99999</v>
       </c>
-      <c r="AH23" s="23" t="s">
+      <c r="AH23" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="AI23" s="40"/>
-      <c r="AJ23" s="27"/>
-      <c r="AK23" s="25"/>
+      <c r="AI23" s="27"/>
+      <c r="AJ23" s="14"/>
+      <c r="AK23" s="12"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A24" s="21">
+      <c r="A24" s="8">
         <v>5</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="12">
         <v>20323088</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F24" s="29"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19">
+      <c r="F24" s="16"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6">
         <v>19</v>
       </c>
-      <c r="N24" s="19">
+      <c r="N24" s="6">
         <v>320</v>
       </c>
-      <c r="O24" s="19">
+      <c r="O24" s="6">
         <v>2525</v>
       </c>
-      <c r="P24" s="19">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="25">
-        <v>2</v>
-      </c>
-      <c r="R24" s="30"/>
-      <c r="S24" s="31" t="s">
+      <c r="P24" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="12">
+        <v>2</v>
+      </c>
+      <c r="R24" s="17"/>
+      <c r="S24" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="T24" s="31" t="s">
+      <c r="T24" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="U24" s="19" t="s">
+      <c r="U24" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="V24" s="20" t="s">
+      <c r="V24" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="W24" s="19"/>
-      <c r="X24" s="21"/>
-      <c r="Y24" s="21"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="22">
+      <c r="W24" s="6"/>
+      <c r="X24" s="8"/>
+      <c r="Y24" s="8"/>
+      <c r="Z24" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA24" s="9">
         <v>3.0703999999999999E-2</v>
       </c>
-      <c r="AB24" s="22">
+      <c r="AB24" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AC24" s="22">
+      <c r="AC24" s="9">
         <v>3.0703999999999999E-2</v>
       </c>
-      <c r="AD24" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE24" s="24">
+      <c r="AD24" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE24" s="11">
         <v>1535.1846479999999</v>
       </c>
-      <c r="AF24" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG24" s="25">
+      <c r="AF24" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG24" s="12">
         <v>99999</v>
       </c>
-      <c r="AH24" s="23" t="s">
+      <c r="AH24" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI24" s="26"/>
-      <c r="AJ24" s="27"/>
-      <c r="AK24" s="25"/>
+      <c r="AI24" s="13"/>
+      <c r="AJ24" s="14"/>
+      <c r="AK24" s="12"/>
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A25" s="32"/>
-      <c r="B25" s="33" t="s">
+      <c r="A25" s="19"/>
+      <c r="B25" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="12">
         <v>20323089</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="34"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="35">
+      <c r="F25" s="21"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="22">
         <v>19</v>
       </c>
-      <c r="N25" s="35">
+      <c r="N25" s="22">
         <v>320</v>
       </c>
-      <c r="O25" s="35">
+      <c r="O25" s="22">
         <v>2525</v>
       </c>
-      <c r="P25" s="35">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="25">
-        <v>2</v>
-      </c>
-      <c r="R25" s="36"/>
-      <c r="S25" s="37" t="s">
+      <c r="P25" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="12">
+        <v>2</v>
+      </c>
+      <c r="R25" s="23"/>
+      <c r="S25" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="T25" s="31"/>
-      <c r="U25" s="25" t="s">
+      <c r="T25" s="18"/>
+      <c r="U25" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="V25" s="25" t="s">
+      <c r="V25" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W25" s="24"/>
-      <c r="X25" s="38"/>
-      <c r="Y25" s="39"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="22">
+      <c r="W25" s="11"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="26"/>
+      <c r="Z25" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA25" s="9">
         <v>3.0703999999999999E-2</v>
       </c>
-      <c r="AB25" s="22">
+      <c r="AB25" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AC25" s="22">
+      <c r="AC25" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AD25" s="25" t="s">
+      <c r="AD25" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE25" s="24">
+      <c r="AE25" s="11">
         <v>1535.1846479999999</v>
       </c>
-      <c r="AF25" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG25" s="25">
+      <c r="AF25" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG25" s="12">
         <v>99999</v>
       </c>
-      <c r="AH25" s="23" t="s">
+      <c r="AH25" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI25" s="40"/>
-      <c r="AJ25" s="27"/>
-      <c r="AK25" s="25"/>
+      <c r="AI25" s="27"/>
+      <c r="AJ25" s="14"/>
+      <c r="AK25" s="12"/>
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A26" s="32"/>
-      <c r="B26" s="33" t="s">
+      <c r="A26" s="19"/>
+      <c r="B26" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="12">
         <v>20323090</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="34"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="35">
+      <c r="F26" s="21"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="22">
         <v>19</v>
       </c>
-      <c r="N26" s="35">
+      <c r="N26" s="22">
         <v>320</v>
       </c>
-      <c r="O26" s="35">
+      <c r="O26" s="22">
         <v>2525</v>
       </c>
-      <c r="P26" s="35">
-        <v>2</v>
-      </c>
-      <c r="Q26" s="25">
-        <v>2</v>
-      </c>
-      <c r="R26" s="36"/>
-      <c r="S26" s="37" t="s">
+      <c r="P26" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="12">
+        <v>2</v>
+      </c>
+      <c r="R26" s="23"/>
+      <c r="S26" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="T26" s="31"/>
-      <c r="U26" s="25" t="s">
+      <c r="T26" s="18"/>
+      <c r="U26" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="V26" s="25" t="s">
+      <c r="V26" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W26" s="24"/>
-      <c r="X26" s="38"/>
-      <c r="Y26" s="39"/>
-      <c r="Z26" s="19"/>
-      <c r="AA26" s="22">
+      <c r="W26" s="11"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="26"/>
+      <c r="Z26" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA26" s="9">
         <v>3.0703999999999999E-2</v>
       </c>
-      <c r="AB26" s="22">
+      <c r="AB26" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AC26" s="22">
+      <c r="AC26" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AD26" s="25" t="s">
+      <c r="AD26" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE26" s="24">
+      <c r="AE26" s="11">
         <v>1535.1846479999999</v>
       </c>
-      <c r="AF26" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG26" s="25">
+      <c r="AF26" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG26" s="12">
         <v>99999</v>
       </c>
-      <c r="AH26" s="23" t="s">
+      <c r="AH26" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI26" s="40"/>
-      <c r="AJ26" s="27"/>
-      <c r="AK26" s="25"/>
+      <c r="AI26" s="27"/>
+      <c r="AJ26" s="14"/>
+      <c r="AK26" s="12"/>
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A27" s="32"/>
-      <c r="B27" s="25" t="s">
+      <c r="A27" s="19"/>
+      <c r="B27" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="12">
         <v>20323091</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="E27" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="41">
+      <c r="F27" s="28">
         <v>0</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="12">
         <v>18</v>
       </c>
-      <c r="H27" s="41">
+      <c r="H27" s="28">
         <v>10</v>
       </c>
-      <c r="I27" s="25">
+      <c r="I27" s="12">
         <v>340</v>
       </c>
-      <c r="J27" s="41">
+      <c r="J27" s="28">
         <v>10</v>
       </c>
-      <c r="K27" s="25">
+      <c r="K27" s="12">
         <v>2440</v>
       </c>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25">
+      <c r="L27" s="12"/>
+      <c r="M27" s="12">
         <v>18</v>
       </c>
-      <c r="N27" s="25">
+      <c r="N27" s="12">
         <v>330</v>
       </c>
-      <c r="O27" s="25">
+      <c r="O27" s="12">
         <v>2430</v>
       </c>
-      <c r="P27" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q27" s="25">
-        <v>2</v>
-      </c>
-      <c r="R27" s="36">
+      <c r="P27" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="12">
+        <v>2</v>
+      </c>
+      <c r="R27" s="23">
         <v>2.9865599999999999E-2</v>
       </c>
-      <c r="S27" s="37" t="s">
+      <c r="S27" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="T27" s="37"/>
-      <c r="U27" s="25" t="s">
+      <c r="T27" s="24"/>
+      <c r="U27" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="V27" s="25" t="s">
+      <c r="V27" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W27" s="24"/>
-      <c r="X27" s="38"/>
-      <c r="Y27" s="39"/>
-      <c r="Z27" s="19"/>
-      <c r="AA27" s="22">
+      <c r="W27" s="11"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="26"/>
+      <c r="Z27" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA27" s="9">
         <v>2.8868399999999999E-2</v>
       </c>
-      <c r="AB27" s="22">
+      <c r="AB27" s="9">
         <v>1.6037999999999999</v>
       </c>
-      <c r="AC27" s="22">
+      <c r="AC27" s="9">
         <v>2.8868399999999999E-2</v>
       </c>
-      <c r="AD27" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE27" s="24">
+      <c r="AD27" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE27" s="11">
         <v>1443.4055658</v>
       </c>
-      <c r="AF27" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG27" s="25">
+      <c r="AF27" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG27" s="12">
         <v>99999</v>
       </c>
-      <c r="AH27" s="23" t="s">
+      <c r="AH27" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AI27" s="40"/>
-      <c r="AJ27" s="27"/>
-      <c r="AK27" s="25"/>
+      <c r="AI27" s="27"/>
+      <c r="AJ27" s="14"/>
+      <c r="AK27" s="12"/>
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A28" s="32"/>
-      <c r="B28" s="25" t="s">
+      <c r="A28" s="19"/>
+      <c r="B28" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="12">
         <v>20323092</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="E28" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="41">
+      <c r="F28" s="28">
         <v>0</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="12">
         <v>18</v>
       </c>
-      <c r="H28" s="41">
+      <c r="H28" s="28">
         <v>10</v>
       </c>
-      <c r="I28" s="25">
+      <c r="I28" s="12">
         <v>340</v>
       </c>
-      <c r="J28" s="41">
+      <c r="J28" s="28">
         <v>10</v>
       </c>
-      <c r="K28" s="25">
+      <c r="K28" s="12">
         <v>165</v>
       </c>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25">
+      <c r="L28" s="12"/>
+      <c r="M28" s="12">
         <v>18</v>
       </c>
-      <c r="N28" s="25">
+      <c r="N28" s="12">
         <v>330</v>
       </c>
-      <c r="O28" s="25">
+      <c r="O28" s="12">
         <v>155</v>
       </c>
-      <c r="P28" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q28" s="25">
-        <v>2</v>
-      </c>
-      <c r="R28" s="36">
+      <c r="P28" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="12">
+        <v>2</v>
+      </c>
+      <c r="R28" s="23">
         <v>2.0195999999999999E-3</v>
       </c>
-      <c r="S28" s="37" t="s">
+      <c r="S28" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="T28" s="37"/>
-      <c r="U28" s="25" t="s">
+      <c r="T28" s="24"/>
+      <c r="U28" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="V28" s="25" t="s">
+      <c r="V28" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W28" s="24"/>
-      <c r="X28" s="38"/>
-      <c r="Y28" s="39"/>
-      <c r="Z28" s="19"/>
-      <c r="AA28" s="22">
+      <c r="W28" s="11"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA28" s="9">
         <v>1.8414E-3</v>
       </c>
-      <c r="AB28" s="22">
+      <c r="AB28" s="9">
         <v>0.1023</v>
       </c>
-      <c r="AC28" s="22">
+      <c r="AC28" s="9">
         <v>1.8414E-3</v>
       </c>
-      <c r="AD28" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE28" s="24">
+      <c r="AD28" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE28" s="11">
         <v>92.069079299999999</v>
       </c>
-      <c r="AF28" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG28" s="25">
+      <c r="AF28" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG28" s="12">
         <v>99999</v>
       </c>
-      <c r="AH28" s="23" t="s">
+      <c r="AH28" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="AI28" s="40"/>
-      <c r="AJ28" s="27"/>
-      <c r="AK28" s="25"/>
+      <c r="AI28" s="27"/>
+      <c r="AJ28" s="14"/>
+      <c r="AK28" s="12"/>
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25" t="s">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="12">
         <v>20323093</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="E29" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="41">
+      <c r="F29" s="28">
         <v>0.1</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="12">
         <v>0.6</v>
       </c>
-      <c r="H29" s="42">
+      <c r="H29" s="29">
         <v>10</v>
       </c>
-      <c r="I29" s="25">
+      <c r="I29" s="12">
         <v>330</v>
       </c>
-      <c r="J29" s="42">
+      <c r="J29" s="29">
         <v>10</v>
       </c>
-      <c r="K29" s="25">
+      <c r="K29" s="12">
         <v>2535</v>
       </c>
-      <c r="L29" s="25"/>
-      <c r="M29" s="25">
+      <c r="L29" s="12"/>
+      <c r="M29" s="12">
         <v>0.5</v>
       </c>
-      <c r="N29" s="25">
+      <c r="N29" s="12">
         <v>320</v>
       </c>
-      <c r="O29" s="25">
+      <c r="O29" s="12">
         <v>2525</v>
       </c>
-      <c r="P29" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q29" s="25">
-        <v>2</v>
-      </c>
-      <c r="R29" s="36"/>
-      <c r="S29" s="37" t="s">
+      <c r="P29" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q29" s="12">
+        <v>2</v>
+      </c>
+      <c r="R29" s="23"/>
+      <c r="S29" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T29" s="31"/>
-      <c r="U29" s="25" t="s">
+      <c r="T29" s="18"/>
+      <c r="U29" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="V29" s="25" t="s">
+      <c r="V29" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W29" s="24"/>
-      <c r="X29" s="38"/>
-      <c r="Y29" s="23"/>
-      <c r="Z29" s="19"/>
-      <c r="AA29" s="22">
+      <c r="W29" s="11"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="10"/>
+      <c r="Z29" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA29" s="9">
         <v>8.0800000000000002E-4</v>
       </c>
-      <c r="AB29" s="22">
+      <c r="AB29" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AC29" s="22">
+      <c r="AC29" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AD29" s="25" t="s">
+      <c r="AD29" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE29" s="24">
+      <c r="AE29" s="11">
         <v>40.399596000000003</v>
       </c>
-      <c r="AF29" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG29" s="25">
+      <c r="AF29" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG29" s="12">
         <v>99999</v>
       </c>
-      <c r="AH29" s="23" t="s">
+      <c r="AH29" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AI29" s="40"/>
-      <c r="AJ29" s="27"/>
-      <c r="AK29" s="25"/>
+      <c r="AI29" s="27"/>
+      <c r="AJ29" s="14"/>
+      <c r="AK29" s="12"/>
     </row>
     <row r="30" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A30" s="32"/>
-      <c r="B30" s="25" t="s">
+      <c r="A30" s="19"/>
+      <c r="B30" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="12">
         <v>20323094</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E30" s="25" t="s">
+      <c r="E30" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="28">
         <v>0.1</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="12">
         <v>0.6</v>
       </c>
-      <c r="H30" s="41">
+      <c r="H30" s="28">
         <v>10</v>
       </c>
-      <c r="I30" s="25">
+      <c r="I30" s="12">
         <v>330</v>
       </c>
-      <c r="J30" s="41">
+      <c r="J30" s="28">
         <v>10</v>
       </c>
-      <c r="K30" s="25">
+      <c r="K30" s="12">
         <v>2535</v>
       </c>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25">
+      <c r="L30" s="12"/>
+      <c r="M30" s="12">
         <v>0.5</v>
       </c>
-      <c r="N30" s="25">
+      <c r="N30" s="12">
         <v>320</v>
       </c>
-      <c r="O30" s="25">
+      <c r="O30" s="12">
         <v>2525</v>
       </c>
-      <c r="P30" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q30" s="25">
-        <v>2</v>
-      </c>
-      <c r="R30" s="36">
+      <c r="P30" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="12">
+        <v>2</v>
+      </c>
+      <c r="R30" s="23">
         <v>1.6731</v>
       </c>
-      <c r="S30" s="37" t="s">
+      <c r="S30" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T30" s="31"/>
-      <c r="U30" s="25" t="s">
+      <c r="T30" s="18"/>
+      <c r="U30" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="V30" s="25" t="s">
+      <c r="V30" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W30" s="24"/>
-      <c r="X30" s="38"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="19"/>
-      <c r="AA30" s="22">
+      <c r="W30" s="11"/>
+      <c r="X30" s="25"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA30" s="9">
         <v>8.0800000000000002E-4</v>
       </c>
-      <c r="AB30" s="22">
+      <c r="AB30" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AC30" s="22">
+      <c r="AC30" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AD30" s="25" t="s">
+      <c r="AD30" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE30" s="24">
+      <c r="AE30" s="11">
         <v>40.399596000000003</v>
       </c>
-      <c r="AF30" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG30" s="25">
+      <c r="AF30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG30" s="12">
         <v>99999</v>
       </c>
-      <c r="AH30" s="23" t="s">
+      <c r="AH30" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AI30" s="40"/>
-      <c r="AJ30" s="27"/>
-      <c r="AK30" s="25"/>
+      <c r="AI30" s="27"/>
+      <c r="AJ30" s="14"/>
+      <c r="AK30" s="12"/>
     </row>
     <row r="31" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A31" s="21">
+      <c r="A31" s="8">
         <v>6</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="12">
         <v>20323095</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F31" s="29"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19">
+      <c r="F31" s="16"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6">
         <v>19</v>
       </c>
-      <c r="N31" s="19">
+      <c r="N31" s="6">
         <v>320</v>
       </c>
-      <c r="O31" s="19">
+      <c r="O31" s="6">
         <v>2525</v>
       </c>
-      <c r="P31" s="19">
-        <v>2</v>
-      </c>
-      <c r="Q31" s="25">
-        <v>2</v>
-      </c>
-      <c r="R31" s="30"/>
-      <c r="S31" s="31" t="s">
+      <c r="P31" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="12">
+        <v>2</v>
+      </c>
+      <c r="R31" s="17"/>
+      <c r="S31" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="T31" s="31" t="s">
+      <c r="T31" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="U31" s="19" t="s">
+      <c r="U31" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="V31" s="20" t="s">
+      <c r="V31" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="W31" s="19"/>
-      <c r="X31" s="21"/>
-      <c r="Y31" s="21"/>
-      <c r="Z31" s="19"/>
-      <c r="AA31" s="22">
+      <c r="W31" s="6"/>
+      <c r="X31" s="8"/>
+      <c r="Y31" s="8"/>
+      <c r="Z31" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA31" s="9">
         <v>3.0703999999999999E-2</v>
       </c>
-      <c r="AB31" s="22">
+      <c r="AB31" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AC31" s="22">
+      <c r="AC31" s="9">
         <v>3.0703999999999999E-2</v>
       </c>
-      <c r="AD31" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE31" s="24">
+      <c r="AD31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE31" s="11">
         <v>1535.1846479999999</v>
       </c>
-      <c r="AF31" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG31" s="25">
+      <c r="AF31" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG31" s="12">
         <v>99999</v>
       </c>
-      <c r="AH31" s="23" t="s">
+      <c r="AH31" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI31" s="26"/>
-      <c r="AJ31" s="27"/>
-      <c r="AK31" s="25"/>
+      <c r="AI31" s="13"/>
+      <c r="AJ31" s="14"/>
+      <c r="AK31" s="12"/>
     </row>
     <row r="32" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A32" s="32"/>
-      <c r="B32" s="33" t="s">
+      <c r="A32" s="19"/>
+      <c r="B32" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="12">
         <v>20323089</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D32" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F32" s="34"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="35">
+      <c r="F32" s="21"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="22">
         <v>19</v>
       </c>
-      <c r="N32" s="35">
+      <c r="N32" s="22">
         <v>320</v>
       </c>
-      <c r="O32" s="35">
+      <c r="O32" s="22">
         <v>2525</v>
       </c>
-      <c r="P32" s="35">
-        <v>2</v>
-      </c>
-      <c r="Q32" s="25">
-        <v>2</v>
-      </c>
-      <c r="R32" s="36"/>
-      <c r="S32" s="37" t="s">
+      <c r="P32" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="12">
+        <v>2</v>
+      </c>
+      <c r="R32" s="23"/>
+      <c r="S32" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="T32" s="31"/>
-      <c r="U32" s="25" t="s">
+      <c r="T32" s="18"/>
+      <c r="U32" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="V32" s="25" t="s">
+      <c r="V32" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W32" s="24"/>
-      <c r="X32" s="38"/>
-      <c r="Y32" s="39"/>
-      <c r="Z32" s="19"/>
-      <c r="AA32" s="22">
+      <c r="W32" s="11"/>
+      <c r="X32" s="25"/>
+      <c r="Y32" s="26"/>
+      <c r="Z32" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA32" s="9">
         <v>3.0703999999999999E-2</v>
       </c>
-      <c r="AB32" s="22">
+      <c r="AB32" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AC32" s="22">
+      <c r="AC32" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AD32" s="25" t="s">
+      <c r="AD32" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE32" s="24">
+      <c r="AE32" s="11">
         <v>1535.1846479999999</v>
       </c>
-      <c r="AF32" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG32" s="25">
+      <c r="AF32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG32" s="12">
         <v>99999</v>
       </c>
-      <c r="AH32" s="23" t="s">
+      <c r="AH32" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI32" s="40"/>
-      <c r="AJ32" s="27"/>
-      <c r="AK32" s="25"/>
+      <c r="AI32" s="27"/>
+      <c r="AJ32" s="14"/>
+      <c r="AK32" s="12"/>
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A33" s="32"/>
-      <c r="B33" s="33" t="s">
+      <c r="A33" s="19"/>
+      <c r="B33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="12">
         <v>20323090</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="34"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="35">
+      <c r="F33" s="21"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="22">
         <v>19</v>
       </c>
-      <c r="N33" s="35">
+      <c r="N33" s="22">
         <v>320</v>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="22">
         <v>2525</v>
       </c>
-      <c r="P33" s="35">
-        <v>2</v>
-      </c>
-      <c r="Q33" s="25">
-        <v>2</v>
-      </c>
-      <c r="R33" s="36"/>
-      <c r="S33" s="37" t="s">
+      <c r="P33" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q33" s="12">
+        <v>2</v>
+      </c>
+      <c r="R33" s="23"/>
+      <c r="S33" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="T33" s="31"/>
-      <c r="U33" s="25" t="s">
+      <c r="T33" s="18"/>
+      <c r="U33" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="V33" s="25" t="s">
+      <c r="V33" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W33" s="24"/>
-      <c r="X33" s="38"/>
-      <c r="Y33" s="39"/>
-      <c r="Z33" s="19"/>
-      <c r="AA33" s="22">
+      <c r="W33" s="11"/>
+      <c r="X33" s="25"/>
+      <c r="Y33" s="26"/>
+      <c r="Z33" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA33" s="9">
         <v>3.0703999999999999E-2</v>
       </c>
-      <c r="AB33" s="22">
+      <c r="AB33" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AC33" s="22">
+      <c r="AC33" s="9">
         <v>1.6160000000000001</v>
       </c>
-      <c r="AD33" s="25" t="s">
+      <c r="AD33" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE33" s="24">
+      <c r="AE33" s="11">
         <v>1535.1846479999999</v>
       </c>
-      <c r="AF33" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG33" s="25">
+      <c r="AF33" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG33" s="12">
         <v>99999</v>
       </c>
-      <c r="AH33" s="23" t="s">
+      <c r="AH33" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI33" s="40"/>
-      <c r="AJ33" s="27"/>
-      <c r="AK33" s="25"/>
+      <c r="AI33" s="27"/>
+      <c r="AJ33" s="14"/>
+      <c r="AK33" s="12"/>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A34" s="32"/>
-      <c r="B34" s="25" t="s">
+      <c r="A34" s="19"/>
+      <c r="B34" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="12">
         <v>20323091</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="E34" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F34" s="41">
+      <c r="F34" s="28">
         <v>0</v>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="12">
         <v>18</v>
       </c>
-      <c r="H34" s="41">
+      <c r="H34" s="28">
         <v>10</v>
       </c>
-      <c r="I34" s="25">
+      <c r="I34" s="12">
         <v>340</v>
       </c>
-      <c r="J34" s="41">
+      <c r="J34" s="28">
         <v>10</v>
       </c>
-      <c r="K34" s="25">
+      <c r="K34" s="12">
         <v>2440</v>
       </c>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25">
+      <c r="L34" s="12"/>
+      <c r="M34" s="12">
         <v>18</v>
       </c>
-      <c r="N34" s="25">
+      <c r="N34" s="12">
         <v>330</v>
       </c>
-      <c r="O34" s="25">
+      <c r="O34" s="12">
         <v>2430</v>
       </c>
-      <c r="P34" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q34" s="25">
-        <v>2</v>
-      </c>
-      <c r="R34" s="36">
+      <c r="P34" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="12">
+        <v>2</v>
+      </c>
+      <c r="R34" s="23">
         <v>2.9865599999999999E-2</v>
       </c>
-      <c r="S34" s="37" t="s">
+      <c r="S34" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="T34" s="37"/>
-      <c r="U34" s="25" t="s">
+      <c r="T34" s="24"/>
+      <c r="U34" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="V34" s="25" t="s">
+      <c r="V34" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W34" s="24"/>
-      <c r="X34" s="38"/>
-      <c r="Y34" s="39"/>
-      <c r="Z34" s="19"/>
-      <c r="AA34" s="22">
+      <c r="W34" s="11"/>
+      <c r="X34" s="25"/>
+      <c r="Y34" s="26"/>
+      <c r="Z34" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA34" s="9">
         <v>2.8868399999999999E-2</v>
       </c>
-      <c r="AB34" s="22">
+      <c r="AB34" s="9">
         <v>1.6037999999999999</v>
       </c>
-      <c r="AC34" s="22">
+      <c r="AC34" s="9">
         <v>2.8868399999999999E-2</v>
       </c>
-      <c r="AD34" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE34" s="24">
+      <c r="AD34" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE34" s="11">
         <v>1443.4055658</v>
       </c>
-      <c r="AF34" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG34" s="25">
+      <c r="AF34" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG34" s="12">
         <v>99999</v>
       </c>
-      <c r="AH34" s="23" t="s">
+      <c r="AH34" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AI34" s="40"/>
-      <c r="AJ34" s="27"/>
-      <c r="AK34" s="25"/>
+      <c r="AI34" s="27"/>
+      <c r="AJ34" s="14"/>
+      <c r="AK34" s="12"/>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A35" s="32"/>
-      <c r="B35" s="25" t="s">
+      <c r="A35" s="19"/>
+      <c r="B35" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="12">
         <v>20323092</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="25" t="s">
+      <c r="E35" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="41">
+      <c r="F35" s="28">
         <v>0</v>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="12">
         <v>18</v>
       </c>
-      <c r="H35" s="41">
+      <c r="H35" s="28">
         <v>10</v>
       </c>
-      <c r="I35" s="25">
+      <c r="I35" s="12">
         <v>340</v>
       </c>
-      <c r="J35" s="41">
+      <c r="J35" s="28">
         <v>10</v>
       </c>
-      <c r="K35" s="25">
+      <c r="K35" s="12">
         <v>165</v>
       </c>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25">
+      <c r="L35" s="12"/>
+      <c r="M35" s="12">
         <v>18</v>
       </c>
-      <c r="N35" s="25">
+      <c r="N35" s="12">
         <v>330</v>
       </c>
-      <c r="O35" s="25">
+      <c r="O35" s="12">
         <v>155</v>
       </c>
-      <c r="P35" s="25">
-        <v>2</v>
-      </c>
-      <c r="Q35" s="25">
-        <v>2</v>
-      </c>
-      <c r="R35" s="36">
+      <c r="P35" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="12">
+        <v>2</v>
+      </c>
+      <c r="R35" s="23">
         <v>2.0195999999999999E-3</v>
       </c>
-      <c r="S35" s="37" t="s">
+      <c r="S35" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="T35" s="37"/>
-      <c r="U35" s="25" t="s">
+      <c r="T35" s="24"/>
+      <c r="U35" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="V35" s="25" t="s">
+      <c r="V35" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W35" s="24"/>
-      <c r="X35" s="38"/>
-      <c r="Y35" s="39"/>
-      <c r="Z35" s="19"/>
-      <c r="AA35" s="22">
+      <c r="W35" s="11"/>
+      <c r="X35" s="25"/>
+      <c r="Y35" s="26"/>
+      <c r="Z35" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA35" s="9">
         <v>1.8414E-3</v>
       </c>
-      <c r="AB35" s="22">
+      <c r="AB35" s="9">
         <v>0.1023</v>
       </c>
-      <c r="AC35" s="22">
+      <c r="AC35" s="9">
         <v>1.8414E-3</v>
       </c>
-      <c r="AD35" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE35" s="24">
+      <c r="AD35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE35" s="11">
         <v>92.069079299999999</v>
       </c>
-      <c r="AF35" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG35" s="25">
+      <c r="AF35" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG35" s="12">
         <v>99999</v>
       </c>
-      <c r="AH35" s="23" t="s">
+      <c r="AH35" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="AI35" s="40"/>
-      <c r="AJ35" s="27"/>
-      <c r="AK35" s="25"/>
+      <c r="AI35" s="27"/>
+      <c r="AJ35" s="14"/>
+      <c r="AK35" s="12"/>
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25" t="s">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="12">
         <v>20323093</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="D36" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E36" s="25" t="s">
+      <c r="E36" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="28">
         <v>0.1</v>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="12">
         <v>0.6</v>
       </c>
-      <c r="H36" s="42">
+      <c r="H36" s="29">
         <v>10</v>
       </c>
-      <c r="I36" s="25">
+      <c r="I36" s="12">
         <v>330</v>
       </c>
-      <c r="J36" s="42">
+      <c r="J36" s="29">
         <v>10</v>
       </c>
-      <c r="K36" s="25">
+      <c r="K36" s="12">
         <v>2535</v>
       </c>
-      <c r="L36" s="25"/>
-      <c r="M36" s="25">
+      <c r="L36" s="12"/>
+      <c r="M36" s="12">
         <v>0.5</v>
       </c>
-      <c r="N36" s="25">
+      <c r="N36" s="12">
         <v>320</v>
       </c>
-      <c r="O36" s="25">
+      <c r="O36" s="12">
         <v>2525</v>
       </c>
-      <c r="P36" s="25">
+      <c r="P36" s="12">
         <v>4</v>
       </c>
-      <c r="Q36" s="25">
+      <c r="Q36" s="12">
         <v>4</v>
       </c>
-      <c r="R36" s="36"/>
-      <c r="S36" s="37" t="s">
+      <c r="R36" s="23"/>
+      <c r="S36" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T36" s="31"/>
-      <c r="U36" s="25" t="s">
+      <c r="T36" s="18"/>
+      <c r="U36" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="V36" s="25" t="s">
+      <c r="V36" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W36" s="24"/>
-      <c r="X36" s="38"/>
-      <c r="Y36" s="23"/>
-      <c r="Z36" s="19"/>
-      <c r="AA36" s="22">
+      <c r="W36" s="11"/>
+      <c r="X36" s="25"/>
+      <c r="Y36" s="10"/>
+      <c r="Z36" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA36" s="9">
         <v>1.616E-3</v>
       </c>
-      <c r="AB36" s="22">
+      <c r="AB36" s="9">
         <v>3.2320000000000002</v>
       </c>
-      <c r="AC36" s="22">
+      <c r="AC36" s="9">
         <v>3.2320000000000002</v>
       </c>
-      <c r="AD36" s="25" t="s">
+      <c r="AD36" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE36" s="24">
+      <c r="AE36" s="11">
         <v>40.399596000000003</v>
       </c>
-      <c r="AF36" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG36" s="25">
+      <c r="AF36" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG36" s="12">
         <v>99999</v>
       </c>
-      <c r="AH36" s="23" t="s">
+      <c r="AH36" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AI36" s="40"/>
-      <c r="AJ36" s="27"/>
-      <c r="AK36" s="25"/>
+      <c r="AI36" s="27"/>
+      <c r="AJ36" s="14"/>
+      <c r="AK36" s="12"/>
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A37" s="32"/>
-      <c r="B37" s="25" t="s">
+      <c r="A37" s="19"/>
+      <c r="B37" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="12">
         <v>20323094</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="25" t="s">
+      <c r="E37" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="F37" s="41">
+      <c r="F37" s="28">
         <v>0.1</v>
       </c>
-      <c r="G37" s="25">
+      <c r="G37" s="12">
         <v>0.6</v>
       </c>
-      <c r="H37" s="41">
+      <c r="H37" s="28">
         <v>10</v>
       </c>
-      <c r="I37" s="25">
+      <c r="I37" s="12">
         <v>330</v>
       </c>
-      <c r="J37" s="41">
+      <c r="J37" s="28">
         <v>10</v>
       </c>
-      <c r="K37" s="25">
+      <c r="K37" s="12">
         <v>2535</v>
       </c>
-      <c r="L37" s="25"/>
-      <c r="M37" s="25">
+      <c r="L37" s="12"/>
+      <c r="M37" s="12">
         <v>0.5</v>
       </c>
-      <c r="N37" s="25">
+      <c r="N37" s="12">
         <v>320</v>
       </c>
-      <c r="O37" s="25">
+      <c r="O37" s="12">
         <v>2525</v>
       </c>
-      <c r="P37" s="25">
+      <c r="P37" s="12">
         <v>4</v>
       </c>
-      <c r="Q37" s="25">
+      <c r="Q37" s="12">
         <v>4</v>
       </c>
-      <c r="R37" s="36">
+      <c r="R37" s="23">
         <v>3.3462000000000001</v>
       </c>
-      <c r="S37" s="37" t="s">
+      <c r="S37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="T37" s="31"/>
-      <c r="U37" s="25" t="s">
+      <c r="T37" s="18"/>
+      <c r="U37" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="V37" s="25" t="s">
+      <c r="V37" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W37" s="24"/>
-      <c r="X37" s="38"/>
-      <c r="Y37" s="23"/>
-      <c r="Z37" s="19"/>
-      <c r="AA37" s="22">
+      <c r="W37" s="11"/>
+      <c r="X37" s="25"/>
+      <c r="Y37" s="10"/>
+      <c r="Z37" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA37" s="9">
         <v>1.616E-3</v>
       </c>
-      <c r="AB37" s="22">
+      <c r="AB37" s="9">
         <v>3.2320000000000002</v>
       </c>
-      <c r="AC37" s="22">
+      <c r="AC37" s="9">
         <v>3.2320000000000002</v>
       </c>
-      <c r="AD37" s="25" t="s">
+      <c r="AD37" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AE37" s="24">
+      <c r="AE37" s="11">
         <v>40.399596000000003</v>
       </c>
-      <c r="AF37" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG37" s="25">
+      <c r="AF37" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG37" s="12">
         <v>99999</v>
       </c>
-      <c r="AH37" s="23" t="s">
+      <c r="AH37" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AI37" s="40"/>
-      <c r="AJ37" s="27"/>
-      <c r="AK37" s="25"/>
+      <c r="AI37" s="27"/>
+      <c r="AJ37" s="14"/>
+      <c r="AK37" s="12"/>
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A38" s="21">
+      <c r="A38" s="8">
         <v>7</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="12">
         <v>20323096</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F38" s="29"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19">
+      <c r="F38" s="16"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6">
         <v>9</v>
       </c>
-      <c r="N38" s="19">
+      <c r="N38" s="6">
         <v>80</v>
       </c>
-      <c r="O38" s="19">
+      <c r="O38" s="6">
         <v>240</v>
       </c>
-      <c r="P38" s="19">
+      <c r="P38" s="6">
         <v>4</v>
       </c>
-      <c r="Q38" s="25">
+      <c r="Q38" s="12">
         <v>4</v>
       </c>
-      <c r="R38" s="30"/>
-      <c r="S38" s="31" t="s">
+      <c r="R38" s="17"/>
+      <c r="S38" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="T38" s="31">
+      <c r="T38" s="18">
         <v>0</v>
       </c>
-      <c r="U38" s="19" t="s">
+      <c r="U38" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="V38" s="20" t="s">
+      <c r="V38" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="W38" s="19"/>
-      <c r="X38" s="21"/>
-      <c r="Y38" s="21"/>
-      <c r="Z38" s="19"/>
-      <c r="AA38" s="22">
+      <c r="W38" s="6"/>
+      <c r="X38" s="8"/>
+      <c r="Y38" s="8"/>
+      <c r="Z38" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA38" s="9">
         <v>6.912E-4</v>
       </c>
-      <c r="AB38" s="22">
+      <c r="AB38" s="9">
         <v>7.6799999999999993E-2</v>
       </c>
-      <c r="AC38" s="22">
+      <c r="AC38" s="9">
         <v>6.912E-4</v>
       </c>
-      <c r="AD38" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE38" s="24">
+      <c r="AD38" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE38" s="11">
         <v>17.2798272</v>
       </c>
-      <c r="AF38" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG38" s="25">
+      <c r="AF38" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG38" s="12">
         <v>99999</v>
       </c>
-      <c r="AH38" s="23" t="s">
+      <c r="AH38" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI38" s="26"/>
-      <c r="AJ38" s="27"/>
-      <c r="AK38" s="25"/>
+      <c r="AI38" s="13"/>
+      <c r="AJ38" s="14"/>
+      <c r="AK38" s="12"/>
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A39" s="32"/>
-      <c r="B39" s="25" t="s">
+      <c r="A39" s="19"/>
+      <c r="B39" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="12">
         <v>20323097</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="25" t="s">
+      <c r="E39" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F39" s="41">
+      <c r="F39" s="28">
         <v>0</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="12">
         <v>9</v>
       </c>
-      <c r="H39" s="41">
+      <c r="H39" s="28">
         <v>10</v>
       </c>
-      <c r="I39" s="25">
+      <c r="I39" s="12">
         <v>90</v>
       </c>
-      <c r="J39" s="41">
+      <c r="J39" s="28">
         <v>10</v>
       </c>
-      <c r="K39" s="25">
+      <c r="K39" s="12">
         <v>250</v>
       </c>
-      <c r="L39" s="25"/>
-      <c r="M39" s="25">
+      <c r="L39" s="12"/>
+      <c r="M39" s="12">
         <v>9</v>
       </c>
-      <c r="N39" s="25">
+      <c r="N39" s="12">
         <v>80</v>
       </c>
-      <c r="O39" s="25">
+      <c r="O39" s="12">
         <v>240</v>
       </c>
-      <c r="P39" s="25">
+      <c r="P39" s="12">
         <v>4</v>
       </c>
-      <c r="Q39" s="25">
+      <c r="Q39" s="12">
         <v>4</v>
       </c>
-      <c r="R39" s="36">
+      <c r="R39" s="23">
         <v>8.0999999999999996E-4</v>
       </c>
-      <c r="S39" s="37" t="s">
+      <c r="S39" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="T39" s="37"/>
-      <c r="U39" s="25" t="s">
+      <c r="T39" s="24"/>
+      <c r="U39" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="V39" s="25" t="s">
+      <c r="V39" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W39" s="24"/>
-      <c r="X39" s="38"/>
-      <c r="Y39" s="39"/>
-      <c r="Z39" s="19"/>
-      <c r="AA39" s="22">
+      <c r="W39" s="11"/>
+      <c r="X39" s="25"/>
+      <c r="Y39" s="26"/>
+      <c r="Z39" s="6">
+        <v>1000</v>
+      </c>
+      <c r="AA39" s="9">
         <v>6.912E-4</v>
       </c>
-      <c r="AB39" s="22">
+      <c r="AB39" s="9">
         <v>7.6799999999999993E-2</v>
       </c>
-      <c r="AC39" s="22">
+      <c r="AC39" s="9">
         <v>6.912E-4</v>
       </c>
-      <c r="AD39" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE39" s="24">
+      <c r="AD39" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE39" s="11">
         <v>17.2798272</v>
       </c>
-      <c r="AF39" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG39" s="25">
+      <c r="AF39" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG39" s="12">
         <v>99999</v>
       </c>
-      <c r="AH39" s="23" t="s">
+      <c r="AH39" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="AI39" s="40"/>
-      <c r="AJ39" s="27"/>
-      <c r="AK39" s="25"/>
+      <c r="AI39" s="27"/>
+      <c r="AJ39" s="14"/>
+      <c r="AK39" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="T1:T2"/>
     <mergeCell ref="AI1:AI2"/>
     <mergeCell ref="AJ1:AJ2"/>
     <mergeCell ref="AK1:AK2"/>
@@ -4350,20 +4436,6 @@
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="W1:W2"/>
     <mergeCell ref="X1:X2"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
